--- a/output/tables/GD/finished tables/Temp1_Global_Fst.xlsx
+++ b/output/tables/GD/finished tables/Temp1_Global_Fst.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\R_WD\revised_bison_popgen\output\tables\GD\finished tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_RWD\revised_bison_popgen\output\tables\GD\finished tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A74F1915-1FF9-4E05-8437-22F0B121EB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1756F6B-8881-441F-941F-44E25E669F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-118" yWindow="-118" windowWidth="20343" windowHeight="12934" xr2:uid="{F28A2329-B764-49D8-98EB-CD1C9E64FFC1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F28A2329-B764-49D8-98EB-CD1C9E64FFC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Temp1_Global_Fst" sheetId="1" r:id="rId1"/>
@@ -608,18 +608,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -631,9 +625,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -641,6 +632,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1019,591 +1025,640 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B34F55-9491-4588-A313-6A22C11F376B}">
   <dimension ref="A1:P18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="6" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.88671875" style="1"/>
+    <col min="16" max="16" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="11"/>
-      <c r="B2" s="9" t="s">
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="9">
         <v>0</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="9">
         <v>0</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="11">
         <v>0.01</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="9">
         <v>0.01</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="11">
         <v>0.01</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="11">
         <v>0.02</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="9">
         <v>0</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="9">
         <v>0</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="9">
         <v>0.01</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="11">
         <v>0.02</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="11">
         <v>0.02</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="11">
         <v>0.02</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="11">
         <v>0.03</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="11">
         <v>0.03</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="11">
         <v>0.03</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="9">
         <v>0</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="11">
         <v>0.01</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="11">
         <v>0.01</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="11">
         <v>0.02</v>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="9">
         <v>0</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="9">
         <v>0.01</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="11">
         <v>0.01</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="11">
         <v>0.01</v>
       </c>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I10" s="9"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="B11" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="C11" s="12">
         <v>0.04</v>
       </c>
-      <c r="D11" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="E11" s="2">
+      <c r="D11" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="E11" s="12">
         <v>0.04</v>
       </c>
-      <c r="F11" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="H11" s="2">
+      <c r="F11" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="H11" s="12">
         <v>0.04</v>
       </c>
-      <c r="I11" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I11" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="12">
         <v>0.06</v>
       </c>
-      <c r="C12" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="D12" s="2">
+      <c r="C12" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="D12" s="12">
         <v>0.06</v>
       </c>
-      <c r="E12" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="G12" s="2">
+      <c r="E12" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="G12" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H12" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="J12" s="2">
+      <c r="H12" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="I12" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="J12" s="12">
         <v>0.03</v>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="12">
         <v>0.06</v>
       </c>
-      <c r="C13" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="D13" s="2">
+      <c r="C13" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="D13" s="12">
         <v>0.06</v>
       </c>
-      <c r="E13" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="F13" s="2">
+      <c r="E13" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="F13" s="12">
         <v>0.06</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="12">
         <v>0.06</v>
       </c>
-      <c r="H13" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="J13" s="2">
+      <c r="H13" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="I13" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="J13" s="12">
         <v>0.02</v>
       </c>
-      <c r="K13" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="K13" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="12">
         <v>0.03</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="12">
         <v>0.03</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="12">
         <v>0.02</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="12">
         <v>0.04</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="12">
         <v>0.03</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="12">
         <v>0.06</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="12">
         <v>0.03</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="12">
         <v>0.03</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="12">
         <v>0.06</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="12">
         <v>0.06</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="12">
         <v>0.06</v>
       </c>
-      <c r="C15" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="D15" s="2">
+      <c r="C15" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="D15" s="12">
         <v>0.06</v>
       </c>
-      <c r="E15" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="G15" s="2">
+      <c r="E15" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="F15" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="G15" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="12">
         <v>0.04</v>
       </c>
-      <c r="I15" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="J15" s="2">
+      <c r="I15" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="J15" s="12">
         <v>0.03</v>
       </c>
-      <c r="K15" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="L15" s="2">
+      <c r="K15" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="L15" s="12">
         <v>0.04</v>
       </c>
-      <c r="M15" s="2">
+      <c r="M15" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="12">
         <v>0.08</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="12">
         <v>0.08</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="12">
         <v>0.1</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="12">
         <v>0.09</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="12">
         <v>0.08</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="12">
         <v>0.09</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="12">
         <v>0.11</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="12">
         <v>0.12</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="12">
         <v>0.11</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16" s="12">
         <v>0.09</v>
       </c>
-      <c r="N16" s="2">
+      <c r="N16" s="12">
         <v>0.13</v>
       </c>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="12">
         <v>0.16</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="12">
         <v>0.16</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="12">
         <v>0.17</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="12">
         <v>0.18</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="12">
         <v>0.13</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="12">
         <v>0.19</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="12">
         <v>0.17</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="12">
         <v>0.14000000000000001</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="12">
         <v>0.21</v>
       </c>
-      <c r="K17" s="2">
+      <c r="K17" s="12">
         <v>0.21</v>
       </c>
-      <c r="L17" s="2">
+      <c r="L17" s="12">
         <v>0.2</v>
       </c>
-      <c r="M17" s="2">
+      <c r="M17" s="12">
         <v>0.17</v>
       </c>
-      <c r="N17" s="2">
+      <c r="N17" s="12">
         <v>0.2</v>
       </c>
-      <c r="O17" s="2">
+      <c r="O17" s="12">
         <v>0.19</v>
       </c>
-      <c r="P17" s="2"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="P17" s="12"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="13">
         <v>0.09</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="13">
         <v>0.11</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="13">
         <v>0.11</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="13">
         <v>0.13</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="13">
         <v>0.08</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="13">
         <v>0.13</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="13">
         <v>0.12</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="13">
         <v>0.09</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="13">
         <v>0.17</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="13">
         <v>0.16</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="13">
         <v>0.16</v>
       </c>
-      <c r="M18" s="8">
+      <c r="M18" s="13">
         <v>0.12</v>
       </c>
-      <c r="N18" s="8">
+      <c r="N18" s="13">
         <v>0.16</v>
       </c>
-      <c r="O18" s="8">
+      <c r="O18" s="13">
         <v>0.15</v>
       </c>
-      <c r="P18" s="8">
+      <c r="P18" s="13">
         <v>0.14000000000000001</v>
       </c>
     </row>

--- a/output/tables/GD/finished tables/Temp1_Global_Fst.xlsx
+++ b/output/tables/GD/finished tables/Temp1_Global_Fst.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_RWD\revised_bison_popgen\output\tables\GD\finished tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\R_WD\revised_bison_popgen\output\tables\GD\finished tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1756F6B-8881-441F-941F-44E25E669F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C8077B-0122-45F4-839B-7FA595E1D42D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F28A2329-B764-49D8-98EB-CD1C9E64FFC1}"/>
+    <workbookView xWindow="-118" yWindow="-118" windowWidth="20343" windowHeight="12934" xr2:uid="{F28A2329-B764-49D8-98EB-CD1C9E64FFC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Temp1_Global_Fst" sheetId="1" r:id="rId1"/>
@@ -46,12 +46,6 @@
     <t>WENT</t>
   </si>
   <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
     <t>EINPW</t>
   </si>
   <si>
@@ -77,13 +71,43 @@
   </si>
   <si>
     <t>n/a</t>
+  </si>
+  <si>
+    <r>
+      <t>C1</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>a</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,6 +250,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -628,12 +659,6 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -647,6 +672,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="19" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1025,34 +1056,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B34F55-9491-4588-A313-6A22C11F376B}">
   <dimension ref="A1:P18"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="6" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.85546875" style="1"/>
+    <col min="16" max="16" width="5.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
@@ -1061,8 +1092,8 @@
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
+    <row r="2" spans="1:16" ht="17.05" x14ac:dyDescent="0.3">
+      <c r="A2" s="13"/>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
@@ -1082,34 +1113,34 @@
         <v>7</v>
       </c>
       <c r="H2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="K2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1122,543 +1153,543 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="7">
         <v>0</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="7">
         <v>0</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="9">
         <v>0.01</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="7">
         <v>0.01</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="9">
         <v>0.01</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="9">
         <v>0.02</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="7">
         <v>0</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="7">
         <v>0</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="7">
         <v>0.01</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <v>0.02</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="9">
         <v>0.02</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <v>0.02</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="9">
         <v>0.03</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <v>0.03</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="9">
         <v>0.03</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="17.05" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="7">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0.01</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0.01</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+    </row>
+    <row r="10" spans="1:16" ht="17.05" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.01</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0.01</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="9">
-        <v>0</v>
-      </c>
-      <c r="C9" s="11">
-        <v>0.01</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="11">
-        <v>0.01</v>
-      </c>
-      <c r="G9" s="11">
+      <c r="B11" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="C11" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="E11" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="F11" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="G11" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="H11" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="I11" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="C12" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="E12" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="F12" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="G12" s="10">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H12" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="I12" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="J12" s="10">
+        <v>0.03</v>
+      </c>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="C13" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="D13" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="E13" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="F13" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="H13" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="I13" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="J13" s="10">
         <v>0.02</v>
       </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
+      <c r="K13" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="9">
-        <v>0</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="E10" s="11">
-        <v>0.01</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="11">
-        <v>0.01</v>
-      </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="10">
+        <v>0.03</v>
+      </c>
+      <c r="C14" s="10">
+        <v>0.03</v>
+      </c>
+      <c r="D14" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="E14" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="F14" s="10">
+        <v>0.03</v>
+      </c>
+      <c r="G14" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="H14" s="10">
+        <v>0.03</v>
+      </c>
+      <c r="I14" s="10">
+        <v>0.03</v>
+      </c>
+      <c r="J14" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="K14" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="L14" s="10">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="C11" s="12">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="C15" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="D15" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="E15" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="G15" s="10">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H15" s="10">
         <v>0.04</v>
       </c>
-      <c r="D11" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="E11" s="12">
+      <c r="I15" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="J15" s="10">
+        <v>0.03</v>
+      </c>
+      <c r="K15" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="L15" s="10">
         <v>0.04</v>
       </c>
-      <c r="F11" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="G11" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="H11" s="12">
-        <v>0.04</v>
-      </c>
-      <c r="I11" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
+      <c r="M15" s="10">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="12">
-        <v>0.06</v>
-      </c>
-      <c r="C12" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="D12" s="12">
-        <v>0.06</v>
-      </c>
-      <c r="E12" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="F12" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="G12" s="12">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="10">
+        <v>0.08</v>
+      </c>
+      <c r="C16" s="10">
+        <v>0.08</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0.09</v>
+      </c>
+      <c r="F16" s="10">
+        <v>0.08</v>
+      </c>
+      <c r="G16" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H12" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="I12" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="J12" s="12">
-        <v>0.03</v>
-      </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
+      <c r="H16" s="10">
+        <v>0.09</v>
+      </c>
+      <c r="I16" s="10">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J16" s="10">
+        <v>0.11</v>
+      </c>
+      <c r="K16" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="L16" s="10">
+        <v>0.11</v>
+      </c>
+      <c r="M16" s="10">
+        <v>0.09</v>
+      </c>
+      <c r="N16" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="12">
-        <v>0.06</v>
-      </c>
-      <c r="C13" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="D13" s="12">
-        <v>0.06</v>
-      </c>
-      <c r="E13" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="F13" s="12">
-        <v>0.06</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0.06</v>
-      </c>
-      <c r="H13" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="I13" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="J13" s="12">
-        <v>0.02</v>
-      </c>
-      <c r="K13" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="10">
+        <v>0.16</v>
+      </c>
+      <c r="C17" s="10">
+        <v>0.16</v>
+      </c>
+      <c r="D17" s="10">
+        <v>0.17</v>
+      </c>
+      <c r="E17" s="10">
+        <v>0.18</v>
+      </c>
+      <c r="F17" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="G17" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="H17" s="10">
+        <v>0.17</v>
+      </c>
+      <c r="I17" s="10">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J17" s="10">
+        <v>0.21</v>
+      </c>
+      <c r="K17" s="10">
+        <v>0.21</v>
+      </c>
+      <c r="L17" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="M17" s="10">
+        <v>0.17</v>
+      </c>
+      <c r="N17" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="O17" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="P17" s="10"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="12">
-        <v>0.03</v>
-      </c>
-      <c r="C14" s="12">
-        <v>0.03</v>
-      </c>
-      <c r="D14" s="12">
-        <v>0.02</v>
-      </c>
-      <c r="E14" s="12">
-        <v>0.04</v>
-      </c>
-      <c r="F14" s="12">
-        <v>0.03</v>
-      </c>
-      <c r="G14" s="12">
-        <v>0.06</v>
-      </c>
-      <c r="H14" s="12">
-        <v>0.03</v>
-      </c>
-      <c r="I14" s="12">
-        <v>0.03</v>
-      </c>
-      <c r="J14" s="12">
-        <v>0.06</v>
-      </c>
-      <c r="K14" s="12">
-        <v>0.06</v>
-      </c>
-      <c r="L14" s="12">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="12">
-        <v>0.06</v>
-      </c>
-      <c r="C15" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="D15" s="12">
-        <v>0.06</v>
-      </c>
-      <c r="E15" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="F15" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="G15" s="12">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="H15" s="12">
-        <v>0.04</v>
-      </c>
-      <c r="I15" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="J15" s="12">
-        <v>0.03</v>
-      </c>
-      <c r="K15" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="L15" s="12">
-        <v>0.04</v>
-      </c>
-      <c r="M15" s="12">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="12"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B18" s="11">
+        <v>0.09</v>
+      </c>
+      <c r="C18" s="11">
+        <v>0.11</v>
+      </c>
+      <c r="D18" s="11">
+        <v>0.11</v>
+      </c>
+      <c r="E18" s="11">
+        <v>0.13</v>
+      </c>
+      <c r="F18" s="11">
         <v>0.08</v>
       </c>
-      <c r="C16" s="12">
-        <v>0.08</v>
-      </c>
-      <c r="D16" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="E16" s="12">
+      <c r="G18" s="11">
+        <v>0.13</v>
+      </c>
+      <c r="H18" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="I18" s="11">
         <v>0.09</v>
       </c>
-      <c r="F16" s="12">
-        <v>0.08</v>
-      </c>
-      <c r="G16" s="12">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="H16" s="12">
-        <v>0.09</v>
-      </c>
-      <c r="I16" s="12">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="J16" s="12">
-        <v>0.11</v>
-      </c>
-      <c r="K16" s="12">
+      <c r="J18" s="11">
+        <v>0.17</v>
+      </c>
+      <c r="K18" s="11">
+        <v>0.16</v>
+      </c>
+      <c r="L18" s="11">
+        <v>0.16</v>
+      </c>
+      <c r="M18" s="11">
         <v>0.12</v>
       </c>
-      <c r="L16" s="12">
-        <v>0.11</v>
-      </c>
-      <c r="M16" s="12">
-        <v>0.09</v>
-      </c>
-      <c r="N16" s="12">
-        <v>0.13</v>
-      </c>
-      <c r="O16" s="12"/>
-      <c r="P16" s="12"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="12">
+      <c r="N18" s="11">
         <v>0.16</v>
       </c>
-      <c r="C17" s="12">
-        <v>0.16</v>
-      </c>
-      <c r="D17" s="12">
-        <v>0.17</v>
-      </c>
-      <c r="E17" s="12">
-        <v>0.18</v>
-      </c>
-      <c r="F17" s="12">
-        <v>0.13</v>
-      </c>
-      <c r="G17" s="12">
-        <v>0.19</v>
-      </c>
-      <c r="H17" s="12">
-        <v>0.17</v>
-      </c>
-      <c r="I17" s="12">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="J17" s="12">
-        <v>0.21</v>
-      </c>
-      <c r="K17" s="12">
-        <v>0.21</v>
-      </c>
-      <c r="L17" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="M17" s="12">
-        <v>0.17</v>
-      </c>
-      <c r="N17" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="O17" s="12">
-        <v>0.19</v>
-      </c>
-      <c r="P17" s="12"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="13">
-        <v>0.09</v>
-      </c>
-      <c r="C18" s="13">
-        <v>0.11</v>
-      </c>
-      <c r="D18" s="13">
-        <v>0.11</v>
-      </c>
-      <c r="E18" s="13">
-        <v>0.13</v>
-      </c>
-      <c r="F18" s="13">
-        <v>0.08</v>
-      </c>
-      <c r="G18" s="13">
-        <v>0.13</v>
-      </c>
-      <c r="H18" s="13">
-        <v>0.12</v>
-      </c>
-      <c r="I18" s="13">
-        <v>0.09</v>
-      </c>
-      <c r="J18" s="13">
-        <v>0.17</v>
-      </c>
-      <c r="K18" s="13">
-        <v>0.16</v>
-      </c>
-      <c r="L18" s="13">
-        <v>0.16</v>
-      </c>
-      <c r="M18" s="13">
-        <v>0.12</v>
-      </c>
-      <c r="N18" s="13">
-        <v>0.16</v>
-      </c>
-      <c r="O18" s="13">
+      <c r="O18" s="11">
         <v>0.15</v>
       </c>
-      <c r="P18" s="13">
+      <c r="P18" s="11">
         <v>0.14000000000000001</v>
       </c>
     </row>
